--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R8" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R9" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>97326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R6" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B7" t="n">
-        <v>97320</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R7" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,7 +1282,7 @@
         <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R6" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>97327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R7" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R8" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R9" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R6" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R7" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R8" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R9" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R6" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R7" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126984444</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R6" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R7" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R8" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R9" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R6" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R7" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R8" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R9" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R8" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R9" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1476,7 +1476,7 @@
         <v>126984444</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R6" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R7" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1279,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R8" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1376,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984481</v>
+        <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863544</v>
+        <v>863584</v>
       </c>
       <c r="R9" t="n">
-        <v>7452104</v>
+        <v>7451900</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -1085,32 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984448</v>
+        <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863218</v>
+        <v>863247</v>
       </c>
       <c r="R6" t="n">
-        <v>7452276</v>
+        <v>7452123</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984456</v>
+        <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863247</v>
+        <v>863218</v>
       </c>
       <c r="R7" t="n">
-        <v>7452123</v>
+        <v>7452276</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>126984443</v>
       </c>
       <c r="B4" t="n">
-        <v>98471</v>
+        <v>98457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>126984458</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>126984456</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>126984448</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>126984481</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>126984457</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126984444</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98308254</v>
+        <v>126984444</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>863616.4619610386</v>
+        <v>863239</v>
       </c>
       <c r="R2" t="n">
-        <v>7451973.283309377</v>
+        <v>7452271</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98308253</v>
+        <v>128469914</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,30 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paljukkavaara, Nb</t>
+          <t>Rajala VP, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>863437.3287800057</v>
+        <v>863303</v>
       </c>
       <c r="R3" t="n">
-        <v>7451831.87144187</v>
+        <v>7451829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -834,7 +831,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Pajala</t>
+          <t>Övertorneå</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -844,27 +841,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Pajala</t>
+          <t>Övertorneå</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,44 +866,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126984443</v>
+        <v>126984456</v>
       </c>
       <c r="B4" t="n">
-        <v>98471</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863592</v>
+        <v>863247</v>
       </c>
       <c r="R4" t="n">
-        <v>7452088</v>
+        <v>7452123</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126984458</v>
+        <v>126984448</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863648</v>
+        <v>863218</v>
       </c>
       <c r="R5" t="n">
-        <v>7451913</v>
+        <v>7452276</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,34 +1072,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126984456</v>
+        <v>98308253</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1120,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863247</v>
+        <v>863437</v>
       </c>
       <c r="R6" t="n">
-        <v>7452123</v>
+        <v>7451832</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1150,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,44 +1153,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126984448</v>
+        <v>126984474</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863218</v>
+        <v>863629</v>
       </c>
       <c r="R7" t="n">
-        <v>7452276</v>
+        <v>7452082</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126984481</v>
+        <v>126984475</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863544</v>
+        <v>863612</v>
       </c>
       <c r="R8" t="n">
-        <v>7452104</v>
+        <v>7452091</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126984457</v>
+        <v>126984481</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863584</v>
+        <v>863544</v>
       </c>
       <c r="R9" t="n">
-        <v>7451900</v>
+        <v>7452104</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1473,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126984444</v>
+        <v>126984457</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1508,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>863239</v>
+        <v>863584</v>
       </c>
       <c r="R10" t="n">
-        <v>7452271</v>
+        <v>7451900</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1546,11 +1529,6 @@
           <t>2025-07-27</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1572,6 +1550,293 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126984458</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Paljukkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>863648</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7451913</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126984443</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Paljukkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>863592</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7452088</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>98308254</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Paljukkavaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>863617</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7451973</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33671-2025 artfynd.xlsx
+++ b/artfynd/A 33671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984444</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984481</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984456</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984457</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984458</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984448</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126984443</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98308253</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,8 +1897,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98308254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>